--- a/Expirimento 2/expiremento2.xlsx
+++ b/Expirimento 2/expiremento2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Documents\resultadoexpiremento2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1772CF00-C93B-404D-A268-6ADA0824007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C03B8B1-32D9-410A-ADAE-C21311DF11D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -781,10 +781,10 @@
         <v>35</v>
       </c>
       <c r="B12" s="3">
+        <v>11290114.300000001</v>
+      </c>
+      <c r="C12" s="3">
         <v>11.683726</v>
-      </c>
-      <c r="C12" s="3">
-        <v>11290114.300000001</v>
       </c>
       <c r="D12" s="3">
         <v>11289279.85</v>
@@ -801,10 +801,10 @@
         <v>36</v>
       </c>
       <c r="B13" s="3">
+        <v>11287318.4</v>
+      </c>
+      <c r="C13" s="3">
         <v>11.468094000000001</v>
-      </c>
-      <c r="C13" s="3">
-        <v>11287318.4</v>
       </c>
       <c r="D13" s="3">
         <v>11288984.92</v>
@@ -821,10 +821,10 @@
         <v>37</v>
       </c>
       <c r="B14" s="3">
+        <v>11293574.300000001</v>
+      </c>
+      <c r="C14" s="3">
         <v>12.651241000000001</v>
-      </c>
-      <c r="C14" s="3">
-        <v>11293574.300000001</v>
       </c>
       <c r="D14" s="3">
         <v>11294937.24</v>
@@ -841,10 +841,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="3">
+        <v>11281314</v>
+      </c>
+      <c r="C15" s="3">
         <v>14.933056000000001</v>
-      </c>
-      <c r="C15" s="3">
-        <v>11281314</v>
       </c>
       <c r="D15" s="3">
         <v>11282674.23</v>
@@ -861,10 +861,10 @@
         <v>39</v>
       </c>
       <c r="B16" s="3">
+        <v>11297206.300000001</v>
+      </c>
+      <c r="C16" s="3">
         <v>15.664707</v>
-      </c>
-      <c r="C16" s="3">
-        <v>11297206.300000001</v>
       </c>
       <c r="D16" s="3">
         <v>11297406.43</v>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="B17" s="3">
+        <v>11282438</v>
+      </c>
+      <c r="C17" s="3">
         <v>13.584182999999999</v>
-      </c>
-      <c r="C17" s="3">
-        <v>11282438</v>
       </c>
       <c r="D17" s="3">
         <v>11282123.939999999</v>
@@ -901,10 +901,10 @@
         <v>41</v>
       </c>
       <c r="B18" s="3">
+        <v>11288487.9</v>
+      </c>
+      <c r="C18" s="3">
         <v>12.717101</v>
-      </c>
-      <c r="C18" s="3">
-        <v>11288487.9</v>
       </c>
       <c r="D18" s="3">
         <v>11287757.880000001</v>
@@ -921,10 +921,10 @@
         <v>42</v>
       </c>
       <c r="B19" s="3">
+        <v>11298109.199999999</v>
+      </c>
+      <c r="C19" s="3">
         <v>13.002034</v>
-      </c>
-      <c r="C19" s="3">
-        <v>11298109.199999999</v>
       </c>
       <c r="D19" s="3">
         <v>11299968.5</v>
@@ -941,10 +941,10 @@
         <v>43</v>
       </c>
       <c r="B20" s="3">
+        <v>11295043.199999999</v>
+      </c>
+      <c r="C20" s="3">
         <v>10.427999</v>
-      </c>
-      <c r="C20" s="3">
-        <v>11295043.199999999</v>
       </c>
       <c r="D20" s="3">
         <v>11292868.17</v>
@@ -961,10 +961,10 @@
         <v>44</v>
       </c>
       <c r="B21" s="3">
+        <v>11305855.6</v>
+      </c>
+      <c r="C21" s="3">
         <v>15.017287</v>
-      </c>
-      <c r="C21" s="3">
-        <v>11305855.6</v>
       </c>
       <c r="D21" s="3">
         <v>11308328.84</v>
